--- a/outputs/computer-product-catalog-review-20260809/TECHM8_Computer_Product_Import_Review.xlsx
+++ b/outputs/computer-product-catalog-review-20260809/TECHM8_Computer_Product_Import_Review.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\program\TECHM8 PRICE LIST\outputs\computer-product-catalog-review-20260809\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC2BDD58-DBD5-4250-BF59-5677DF78357B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1204DC8-3BCD-437A-8351-B5C3634D93FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4590" yWindow="2460" windowWidth="22365" windowHeight="12315" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -6497,51 +6497,51 @@
         <v>223</v>
       </c>
     </row>
-    <row r="72" spans="1:14" ht="29.25">
-      <c r="A72" s="6" t="s">
+    <row r="72" spans="1:14" s="23" customFormat="1" ht="29.25">
+      <c r="A72" s="19" t="s">
         <v>224</v>
       </c>
-      <c r="B72" s="9" t="str">
+      <c r="B72" s="20" t="str">
         <f>"TM8-COMP-10041"</f>
         <v>TM8-COMP-10041</v>
       </c>
-      <c r="C72" s="6" t="s">
+      <c r="C72" s="19" t="s">
         <v>225</v>
       </c>
-      <c r="D72" s="6" t="s">
+      <c r="D72" s="19" t="s">
         <v>226</v>
       </c>
-      <c r="E72" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="F72" s="6" t="s">
+      <c r="E72" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="F72" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="G72" s="8">
-        <v>0</v>
-      </c>
-      <c r="H72" s="7">
-        <v>0</v>
-      </c>
-      <c r="I72" s="8">
+      <c r="G72" s="21">
+        <v>0</v>
+      </c>
+      <c r="H72" s="22">
+        <v>0</v>
+      </c>
+      <c r="I72" s="21">
         <v>159</v>
       </c>
-      <c r="J72" s="7">
+      <c r="J72" s="22">
         <v>159</v>
       </c>
-      <c r="K72" s="6" t="str">
+      <c r="K72" s="19" t="str">
         <f t="shared" si="4"/>
         <v>MISSING</v>
       </c>
-      <c r="L72" s="6" t="str">
+      <c r="L72" s="19" t="str">
         <f t="shared" si="5"/>
         <v>OK</v>
       </c>
-      <c r="M72" s="6" t="str">
+      <c r="M72" s="19" t="str">
         <f>IF('Product Review'!U77="","MISSING","FOUND")</f>
         <v>MISSING</v>
       </c>
-      <c r="N72" s="6" t="s">
+      <c r="N72" s="19" t="s">
         <v>227</v>
       </c>
     </row>
